--- a/Financial Analysis/ERJ.xlsx
+++ b/Financial Analysis/ERJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030B7B74-265F-4F4C-A97C-5322941629C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D747E3D6-5D9C-45E7-B84D-B116121220F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{26DC2385-0FD0-4A26-A38A-609A05E20FB8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{26DC2385-0FD0-4A26-A38A-609A05E20FB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>ERJ</t>
   </si>
@@ -243,16 +243,26 @@
   </si>
   <si>
     <t>Overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +312,15 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -344,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -363,6 +382,8 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,14 +831,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>57.19</v>
+        <v>57.35</v>
       </c>
       <c r="E3" s="4">
-        <v>45903</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45903</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="4">
         <v>45965</v>
@@ -841,7 +862,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>10494.365</v>
+        <v>10523.725</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -883,7 +904,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>11094.365</v>
+        <v>11123.725</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{875AC1A7-EE29-4764-83A3-E8C5C7FED37C}">
-  <dimension ref="B2:EJ35"/>
+  <dimension ref="B2:EJ39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1212,43 +1233,43 @@
         <v>25</v>
       </c>
       <c r="C5" s="9">
-        <f>C3-C4</f>
+        <f t="shared" ref="C5:L5" si="2">C3-C4</f>
         <v>113.70000000000005</v>
       </c>
       <c r="D5" s="9">
-        <f>D3-D4</f>
+        <f t="shared" si="2"/>
         <v>223.29999999999995</v>
       </c>
       <c r="E5" s="9">
-        <f>E3-E4</f>
+        <f t="shared" si="2"/>
         <v>233.10000000000014</v>
       </c>
       <c r="F5" s="9">
-        <f>F3-F4</f>
+        <f t="shared" si="2"/>
         <v>339.5</v>
       </c>
       <c r="G5" s="9">
-        <f>G3-G4</f>
+        <f t="shared" si="2"/>
         <v>168.70000000000005</v>
       </c>
       <c r="H5" s="9">
-        <f>H3-H4</f>
+        <f t="shared" si="2"/>
         <v>240</v>
       </c>
       <c r="I5" s="9">
-        <f>I3-I4</f>
+        <f t="shared" si="2"/>
         <v>314.80000000000018</v>
       </c>
       <c r="J5" s="9">
-        <f>J3-J4</f>
+        <f t="shared" si="2"/>
         <v>429.59999999999991</v>
       </c>
       <c r="K5" s="9">
-        <f>K3-K4</f>
+        <f t="shared" si="2"/>
         <v>189.10000000000002</v>
       </c>
       <c r="L5" s="9">
-        <f>L3-L4</f>
+        <f t="shared" si="2"/>
         <v>352.90000000000009</v>
       </c>
       <c r="M5" s="9">
@@ -1260,31 +1281,31 @@
         <v>527.02199999999993</v>
       </c>
       <c r="P5" s="9">
-        <f>P3-P4</f>
+        <f t="shared" ref="P5:V5" si="3">P3-P4</f>
         <v>795.5</v>
       </c>
       <c r="Q5" s="9">
-        <f>Q3-Q4</f>
+        <f t="shared" si="3"/>
         <v>477.59999999999991</v>
       </c>
       <c r="R5" s="9">
-        <f>R3-R4</f>
+        <f t="shared" si="3"/>
         <v>659.59999999999991</v>
       </c>
       <c r="S5" s="9">
-        <f>S3-S4</f>
+        <f t="shared" si="3"/>
         <v>912</v>
       </c>
       <c r="T5" s="9">
-        <f>T3-T4</f>
+        <f t="shared" si="3"/>
         <v>909.60000000000036</v>
       </c>
       <c r="U5" s="9">
-        <f>U3-U4</f>
+        <f t="shared" si="3"/>
         <v>1153.1000000000004</v>
       </c>
       <c r="V5" s="9">
-        <f>V3-V4</f>
+        <f t="shared" si="3"/>
         <v>1458.1047600000002</v>
       </c>
       <c r="W5" s="9">
@@ -1292,39 +1313,39 @@
         <v>1692.021174</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" ref="X5:AF5" si="2">X3*0.19</f>
+        <f t="shared" ref="X5:AF5" si="4">X3*0.19</f>
         <v>1878.1435031400001</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2009.6135483598002</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2110.0942257777901</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2173.397052551124</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2216.8649936021466</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2261.2022934741894</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2306.4263393436736</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2352.554866130547</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2399.605963453158</v>
       </c>
     </row>
@@ -1383,15 +1404,15 @@
         <v>184.9</v>
       </c>
       <c r="T6" s="6">
-        <f t="shared" ref="S6:V13" si="3">SUM(C6:F6)</f>
+        <f t="shared" ref="T6:U13" si="5">SUM(C6:F6)</f>
         <v>204.9</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" ref="U6:V13" si="4">SUM(G6:J6)</f>
+        <f t="shared" ref="U6:U13" si="6">SUM(G6:J6)</f>
         <v>198.89999999999998</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" ref="V6:V13" si="5">SUM(K6:N6)</f>
+        <f t="shared" ref="V6:V13" si="7">SUM(K6:N6)</f>
         <v>206.75400000000002</v>
       </c>
       <c r="W6" s="6">
@@ -1399,39 +1420,39 @@
         <v>212.95662000000002</v>
       </c>
       <c r="X6" s="6">
-        <f t="shared" ref="X6:AF6" si="6">W6*1.03</f>
+        <f t="shared" ref="X6:AF6" si="8">W6*1.03</f>
         <v>219.34531860000001</v>
       </c>
       <c r="Y6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>225.92567815800001</v>
       </c>
       <c r="Z6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>232.70344850274003</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>239.68455195782224</v>
       </c>
       <c r="AB6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>246.8750885165569</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>254.2813411720536</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>261.90978140721523</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>269.76707484943171</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>277.86008709491466</v>
       </c>
     </row>
@@ -1490,15 +1511,15 @@
         <v>274.39999999999998</v>
       </c>
       <c r="T7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>314.7</v>
       </c>
       <c r="U7" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>309.70000000000005</v>
       </c>
       <c r="V7" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>349.13418000000001</v>
       </c>
       <c r="W7" s="6">
@@ -1506,39 +1527,39 @@
         <v>391.83648239999997</v>
       </c>
       <c r="X7" s="6">
-        <f t="shared" ref="X7:AF7" si="7">X3*0.044</f>
+        <f t="shared" ref="X7:AF7" si="9">X3*0.044</f>
         <v>434.93849546399997</v>
       </c>
       <c r="Y7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>465.38419014648002</v>
       </c>
       <c r="Z7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>488.653399653804</v>
       </c>
       <c r="AA7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>503.31300164341815</v>
       </c>
       <c r="AB7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>513.37926167628655</v>
       </c>
       <c r="AC7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>523.64684690981233</v>
       </c>
       <c r="AD7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>534.11978384800852</v>
       </c>
       <c r="AE7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>544.80217952496878</v>
       </c>
       <c r="AF7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>555.69822311546818</v>
       </c>
     </row>
@@ -1595,15 +1616,15 @@
         <v>17.399999999999999</v>
       </c>
       <c r="T8" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-10.199999999999999</v>
       </c>
       <c r="U8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21.099999999999998</v>
       </c>
       <c r="V8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5.8999999999999995</v>
       </c>
       <c r="W8" s="6">
@@ -1692,15 +1713,15 @@
         <v>110</v>
       </c>
       <c r="T9" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>90.3</v>
       </c>
       <c r="U9" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>55</v>
       </c>
       <c r="V9" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>56.66</v>
       </c>
       <c r="W9" s="6">
@@ -1708,39 +1729,39 @@
         <v>58.3598</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" ref="X9:AF9" si="8">W9*1.03</f>
+        <f t="shared" ref="X9:AF9" si="10">W9*1.03</f>
         <v>60.110593999999999</v>
       </c>
       <c r="Y9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>61.913911820000003</v>
       </c>
       <c r="Z9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>63.771329174600005</v>
       </c>
       <c r="AA9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>65.684469049838</v>
       </c>
       <c r="AB9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>67.655003121333138</v>
       </c>
       <c r="AC9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>69.684653214973139</v>
       </c>
       <c r="AD9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>71.775192811422329</v>
       </c>
       <c r="AE9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>73.928448595765005</v>
       </c>
       <c r="AF9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>76.146302053637953</v>
       </c>
     </row>
@@ -1783,15 +1804,15 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-155.5</v>
       </c>
       <c r="U10" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-278.39999999999998</v>
       </c>
       <c r="V10" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-41.7</v>
       </c>
       <c r="W10" s="6">
@@ -1864,15 +1885,15 @@
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
       <c r="T11" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>146.19999999999999</v>
       </c>
       <c r="U11" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>175</v>
       </c>
       <c r="V11" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>55.4</v>
       </c>
       <c r="W11" s="6">
@@ -1914,39 +1935,39 @@
         <v>15</v>
       </c>
       <c r="D12" s="6">
-        <f t="shared" ref="D12:L12" si="9">SUM(D10:D11)</f>
+        <f t="shared" ref="D12:L12" si="11">SUM(D10:D11)</f>
         <v>8.5000000000000036</v>
       </c>
       <c r="E12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>9.3000000000000043</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-27.100000000000009</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>30.199999999999996</v>
       </c>
       <c r="H12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-27.299999999999997</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-108</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.6999999999999993</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>9.5</v>
       </c>
       <c r="M12" s="6"/>
@@ -1964,15 +1985,15 @@
         <v>444.5</v>
       </c>
       <c r="T12" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.7000000000000028</v>
       </c>
       <c r="U12" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20.899999999999995</v>
       </c>
       <c r="V12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>13.7</v>
       </c>
       <c r="W12" s="6">
@@ -2055,15 +2076,15 @@
         <v>-8.5</v>
       </c>
       <c r="T13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-10.199999999999999</v>
       </c>
       <c r="U13" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.3</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
       <c r="W13" s="6">
@@ -2106,39 +2127,39 @@
         <v>166.00000000000003</v>
       </c>
       <c r="D14" s="6">
-        <f t="shared" ref="D14:L14" si="10">SUM(D6:D13)-D12</f>
+        <f t="shared" ref="D14:L14" si="12">SUM(D6:D13)-D12</f>
         <v>150.1</v>
       </c>
       <c r="E14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>148.69999999999999</v>
       </c>
       <c r="F14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>130.4</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>172.60000000000002</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>112.1</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>29.599999999999994</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>171.29999999999998</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>137.89999999999998</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>173.4</v>
       </c>
       <c r="M14" s="6"/>
@@ -2176,39 +2197,39 @@
         <v>663.1529023999999</v>
       </c>
       <c r="X14" s="6">
-        <f t="shared" ref="X14:AF14" si="11">SUM(X6:X13)-X10-X11</f>
+        <f t="shared" ref="X14:AF14" si="13">SUM(X6:X13)-X10-X11</f>
         <v>714.394408064</v>
       </c>
       <c r="Y14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>753.22378012447996</v>
       </c>
       <c r="Z14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>785.12817733114412</v>
       </c>
       <c r="AA14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>808.68202265107834</v>
       </c>
       <c r="AB14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>827.90935331417666</v>
       </c>
       <c r="AC14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>847.61284129683918</v>
       </c>
       <c r="AD14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>867.80475806664617</v>
       </c>
       <c r="AE14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>888.49770297016551</v>
       </c>
       <c r="AF14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>909.70461226402085</v>
       </c>
     </row>
@@ -2217,113 +2238,113 @@
         <v>33</v>
       </c>
       <c r="C15" s="9">
-        <f>C5-C14</f>
+        <f t="shared" ref="C15:L15" si="14">C5-C14</f>
         <v>-52.299999999999983</v>
       </c>
       <c r="D15" s="9">
-        <f>D5-D14</f>
+        <f t="shared" si="14"/>
         <v>73.19999999999996</v>
       </c>
       <c r="E15" s="9">
-        <f>E5-E14</f>
+        <f t="shared" si="14"/>
         <v>84.400000000000148</v>
       </c>
       <c r="F15" s="9">
-        <f>F5-F14</f>
+        <f t="shared" si="14"/>
         <v>209.1</v>
       </c>
       <c r="G15" s="9">
-        <f>G5-G14</f>
+        <f t="shared" si="14"/>
         <v>-3.8999999999999773</v>
       </c>
       <c r="H15" s="9">
-        <f>H5-H14</f>
+        <f t="shared" si="14"/>
         <v>127.9</v>
       </c>
       <c r="I15" s="9">
-        <f>I5-I14</f>
+        <f t="shared" si="14"/>
         <v>285.20000000000016</v>
       </c>
       <c r="J15" s="9">
-        <f>J5-J14</f>
+        <f t="shared" si="14"/>
         <v>258.29999999999995</v>
       </c>
       <c r="K15" s="9">
-        <f>K5-K14</f>
+        <f t="shared" si="14"/>
         <v>51.200000000000045</v>
       </c>
       <c r="L15" s="9">
-        <f>L5-L14</f>
+        <f t="shared" si="14"/>
         <v>179.50000000000009</v>
       </c>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="P15" s="9">
-        <f>P5-P14</f>
+        <f t="shared" ref="P15:W15" si="15">P5-P14</f>
         <v>-77</v>
       </c>
       <c r="Q15" s="9">
-        <f>Q5-Q14</f>
+        <f t="shared" si="15"/>
         <v>-323.40000000000009</v>
       </c>
       <c r="R15" s="9">
-        <f>R5-R14</f>
+        <f t="shared" si="15"/>
         <v>201.2999999999999</v>
       </c>
       <c r="S15" s="9">
-        <f>S5-S14</f>
+        <f t="shared" si="15"/>
         <v>-110.69999999999982</v>
       </c>
       <c r="T15" s="9">
-        <f>T5-T14</f>
+        <f t="shared" si="15"/>
         <v>314.40000000000032</v>
       </c>
       <c r="U15" s="9">
-        <f>U5-U14</f>
+        <f t="shared" si="15"/>
         <v>543.20000000000027</v>
       </c>
       <c r="V15" s="9">
-        <f>V5-V14</f>
+        <f t="shared" si="15"/>
         <v>822.35658000000012</v>
       </c>
       <c r="W15" s="9">
-        <f>W5-W14</f>
+        <f t="shared" si="15"/>
         <v>1028.8682716000001</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" ref="X15:AF15" si="12">X5-X14</f>
+        <f t="shared" ref="X15:AF15" si="16">X5-X14</f>
         <v>1163.7490950760002</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1256.3897682353204</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1324.966048446646</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1364.7150299000457</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1388.9556402879698</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1413.5894521773503</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1438.6215812770274</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1464.0571631603816</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1489.9013511891371</v>
       </c>
     </row>
@@ -2376,15 +2397,15 @@
         <v>-121.9</v>
       </c>
       <c r="T16" s="6">
-        <f t="shared" ref="S16:T18" si="13">SUM(C16:F16)</f>
+        <f t="shared" ref="T16:T18" si="17">SUM(C16:F16)</f>
         <v>-128.6</v>
       </c>
       <c r="U16" s="6">
-        <f t="shared" ref="U16:V18" si="14">SUM(G16:J16)</f>
+        <f t="shared" ref="U16:U18" si="18">SUM(G16:J16)</f>
         <v>-311.10000000000002</v>
       </c>
       <c r="V16" s="6">
-        <f t="shared" ref="V16:V18" si="15">SUM(K16:N16)</f>
+        <f t="shared" ref="V16:V18" si="19">SUM(K16:N16)</f>
         <v>-116.4</v>
       </c>
       <c r="W16" s="6">
@@ -2392,39 +2413,39 @@
         <v>-118.72800000000001</v>
       </c>
       <c r="X16" s="6">
-        <f t="shared" ref="X16:AF16" si="16">W16*1.02</f>
+        <f t="shared" ref="X16:AF16" si="20">W16*1.02</f>
         <v>-121.10256000000001</v>
       </c>
       <c r="Y16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-123.52461120000001</v>
       </c>
       <c r="Z16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-125.99510342400001</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-128.51500549248001</v>
       </c>
       <c r="AB16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-131.08530560232961</v>
       </c>
       <c r="AC16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-133.70701171437619</v>
       </c>
       <c r="AD16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-136.38115194866373</v>
       </c>
       <c r="AE16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-139.10877498763699</v>
       </c>
       <c r="AF16" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-141.89095048738974</v>
       </c>
     </row>
@@ -2477,15 +2498,15 @@
         <v>245.4</v>
       </c>
       <c r="T17" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>321.89999999999998</v>
       </c>
       <c r="U17" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>415.6</v>
       </c>
       <c r="V17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>295.5</v>
       </c>
       <c r="W17" s="6">
@@ -2493,39 +2514,39 @@
         <v>301.41000000000003</v>
       </c>
       <c r="X17" s="6">
-        <f t="shared" ref="X17:AF17" si="17">W17*1.02</f>
+        <f t="shared" ref="X17:AF17" si="21">W17*1.02</f>
         <v>307.43820000000005</v>
       </c>
       <c r="Y17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>313.58696400000008</v>
       </c>
       <c r="Z17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>319.8587032800001</v>
       </c>
       <c r="AA17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>326.25587734560008</v>
       </c>
       <c r="AB17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>332.78099489251207</v>
       </c>
       <c r="AC17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>339.43661479036234</v>
       </c>
       <c r="AD17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>346.22534708616962</v>
       </c>
       <c r="AE17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>353.14985402789301</v>
       </c>
       <c r="AF17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>360.21285110845088</v>
       </c>
     </row>
@@ -2578,15 +2599,15 @@
         <v>-28.2</v>
       </c>
       <c r="T18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.49999999999999956</v>
       </c>
       <c r="U18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>5.9999999999999982</v>
       </c>
       <c r="V18" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>28.5</v>
       </c>
       <c r="W18" s="6">
@@ -2625,113 +2646,113 @@
         <v>37</v>
       </c>
       <c r="C19" s="9">
-        <f>C15-C16-C17-C18</f>
+        <f t="shared" ref="C19:L19" si="22">C15-C16-C17-C18</f>
         <v>-103.39999999999998</v>
       </c>
       <c r="D19" s="9">
-        <f>D15-D16-D17-D18</f>
+        <f t="shared" si="22"/>
         <v>-0.80000000000003135</v>
       </c>
       <c r="E19" s="9">
-        <f>E15-E16-E17-E18</f>
+        <f t="shared" si="22"/>
         <v>57.200000000000145</v>
       </c>
       <c r="F19" s="9">
-        <f>F15-F16-F17-F18</f>
+        <f t="shared" si="22"/>
         <v>167.6</v>
       </c>
       <c r="G19" s="9">
-        <f>G15-G16-G17-G18</f>
+        <f t="shared" si="22"/>
         <v>33.000000000000028</v>
       </c>
       <c r="H19" s="9">
-        <f>H15-H16-H17-H18</f>
+        <f t="shared" si="22"/>
         <v>111.4</v>
       </c>
       <c r="I19" s="9">
-        <f>I15-I16-I17-I18</f>
+        <f t="shared" si="22"/>
         <v>244.00000000000014</v>
       </c>
       <c r="J19" s="9">
-        <f>J15-J16-J17-J18</f>
+        <f t="shared" si="22"/>
         <v>168.59999999999994</v>
       </c>
       <c r="K19" s="9">
-        <f>K15-K16-K17-K18</f>
+        <f t="shared" si="22"/>
         <v>-24.099999999999948</v>
       </c>
       <c r="L19" s="9">
-        <f>L15-L16-L17-L18</f>
+        <f t="shared" si="22"/>
         <v>47.200000000000088</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="P19" s="9">
-        <f>P15-P16-P17-P18</f>
+        <f t="shared" ref="P19:W19" si="23">P15-P16-P17-P18</f>
         <v>-186.2</v>
       </c>
       <c r="Q19" s="9">
-        <f>Q15-Q16-Q17-Q18</f>
+        <f t="shared" si="23"/>
         <v>-635.20000000000016</v>
       </c>
       <c r="R19" s="9">
-        <f>R15-R16-R17-R18</f>
+        <f t="shared" si="23"/>
         <v>27.399999999999864</v>
       </c>
       <c r="S19" s="9">
-        <f>S15-S16-S17-S18</f>
+        <f t="shared" si="23"/>
         <v>-205.99999999999983</v>
       </c>
       <c r="T19" s="9">
-        <f>T15-T16-T17-T18</f>
+        <f t="shared" si="23"/>
         <v>120.60000000000036</v>
       </c>
       <c r="U19" s="9">
-        <f>U15-U16-U17-U18</f>
+        <f t="shared" si="23"/>
         <v>432.70000000000027</v>
       </c>
       <c r="V19" s="9">
-        <f>V15-V16-V17-V18</f>
+        <f t="shared" si="23"/>
         <v>614.7565800000001</v>
       </c>
       <c r="W19" s="9">
-        <f>W15-W16-W17-W18</f>
+        <f t="shared" si="23"/>
         <v>846.18627160000005</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" ref="X19:AF19" si="18">X15-X16-X17-X18</f>
+        <f t="shared" ref="X19:AF19" si="24">X15-X16-X17-X18</f>
         <v>977.41345507600022</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1066.3274154353203</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1131.102448590646</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1166.9741580469256</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1187.2599509977872</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1207.859849101364</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1228.7773861395215</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1250.0160841201255</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>1271.579450568076</v>
       </c>
     </row>
@@ -2784,15 +2805,15 @@
         <v>-2.2999999999999998</v>
       </c>
       <c r="T20" s="6">
-        <f t="shared" ref="S20:T21" si="19">SUM(C20:F20)</f>
+        <f t="shared" ref="T20:T21" si="25">SUM(C20:F20)</f>
         <v>-43.6</v>
       </c>
       <c r="U20" s="6">
-        <f t="shared" ref="U20:V21" si="20">SUM(G20:J20)</f>
+        <f t="shared" ref="U20:U21" si="26">SUM(G20:J20)</f>
         <v>202.39999999999998</v>
       </c>
       <c r="V20" s="6">
-        <f t="shared" ref="V20:V21" si="21">SUM(K20:N20)</f>
+        <f t="shared" ref="V20:V21" si="27">SUM(K20:N20)</f>
         <v>-126</v>
       </c>
       <c r="W20" s="6">
@@ -2800,39 +2821,39 @@
         <v>126.92794074</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" ref="X20:AF20" si="22">X19*0.15</f>
+        <f t="shared" ref="X20:AF20" si="28">X19*0.15</f>
         <v>146.61201826140004</v>
       </c>
       <c r="Y20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>159.94911231529804</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>169.66536728859688</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>175.04612370703884</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>178.08899264966809</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>181.17897736520459</v>
       </c>
       <c r="AD20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>184.31660792092822</v>
       </c>
       <c r="AE20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>187.50241261801881</v>
       </c>
       <c r="AF20" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>190.73691758521139</v>
       </c>
     </row>
@@ -2885,15 +2906,15 @@
         <v>-18.100000000000001</v>
       </c>
       <c r="T21" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>0.30000000000000071</v>
       </c>
       <c r="U21" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>2.1000000000000014</v>
       </c>
       <c r="V21" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-2.9000000000000004</v>
       </c>
       <c r="W21" s="6">
@@ -2932,113 +2953,113 @@
         <v>40</v>
       </c>
       <c r="C22" s="9">
-        <f>C19-C20-C21</f>
+        <f t="shared" ref="C22:L22" si="29">C19-C20-C21</f>
         <v>-70.999999999999972</v>
       </c>
       <c r="D22" s="9">
-        <f>D19-D20-D21</f>
+        <f t="shared" si="29"/>
         <v>-18.800000000000033</v>
       </c>
       <c r="E22" s="9">
-        <f>E19-E20-E21</f>
+        <f t="shared" si="29"/>
         <v>61.000000000000142</v>
       </c>
       <c r="F22" s="9">
-        <f>F19-F20-F21</f>
+        <f t="shared" si="29"/>
         <v>192.70000000000002</v>
       </c>
       <c r="G22" s="9">
-        <f>G19-G20-G21</f>
+        <f t="shared" si="29"/>
         <v>28.700000000000028</v>
       </c>
       <c r="H22" s="9">
-        <f>H19-H20-H21</f>
+        <f t="shared" si="29"/>
         <v>99.4</v>
       </c>
       <c r="I22" s="9">
-        <f>I19-I20-I21</f>
+        <f t="shared" si="29"/>
         <v>178.80000000000015</v>
       </c>
       <c r="J22" s="9">
-        <f>J19-J20-J21</f>
+        <f t="shared" si="29"/>
         <v>45.599999999999945</v>
       </c>
       <c r="K22" s="9">
-        <f>K19-K20-K21</f>
+        <f t="shared" si="29"/>
         <v>73.400000000000048</v>
       </c>
       <c r="L22" s="9">
-        <f>L19-L20-L21</f>
+        <f t="shared" si="29"/>
         <v>78.600000000000094</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="P22" s="9">
-        <f>P19-P20-P21</f>
+        <f t="shared" ref="P22:W22" si="30">P19-P20-P21</f>
         <v>-322.3</v>
       </c>
       <c r="Q22" s="9">
-        <f>Q19-Q20-Q21</f>
+        <f t="shared" si="30"/>
         <v>-731.9000000000002</v>
       </c>
       <c r="R22" s="9">
-        <f>R19-R20-R21</f>
+        <f t="shared" si="30"/>
         <v>-44.700000000000145</v>
       </c>
       <c r="S22" s="9">
-        <f>S19-S20-S21</f>
+        <f t="shared" si="30"/>
         <v>-185.59999999999982</v>
       </c>
       <c r="T22" s="9">
-        <f>T19-T20-T21</f>
+        <f t="shared" si="30"/>
         <v>163.90000000000035</v>
       </c>
       <c r="U22" s="9">
-        <f>U19-U20-U21</f>
+        <f t="shared" si="30"/>
         <v>228.2000000000003</v>
       </c>
       <c r="V22" s="9">
-        <f>V19-V20-V21</f>
+        <f t="shared" si="30"/>
         <v>743.65658000000008</v>
       </c>
       <c r="W22" s="9">
-        <f>W19-W20-W21</f>
+        <f t="shared" si="30"/>
         <v>719.25833086000011</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22:AF22" si="23">X19-X20-X21</f>
+        <f t="shared" ref="X22:AF22" si="31">X19-X20-X21</f>
         <v>830.80143681460015</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>906.37830312002222</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>961.43708130204914</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>991.92803433988672</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>1009.1709583481191</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>1026.6808717361594</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>1044.4607782185933</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>1062.5136715021067</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>1080.8425329828647</v>
       </c>
       <c r="AG22" s="2">
@@ -3046,431 +3067,431 @@
         <v>1070.034107653036</v>
       </c>
       <c r="AH22" s="2">
-        <f t="shared" ref="AH22:CS22" si="24">AG22*(1+$AI$27)</f>
+        <f t="shared" ref="AH22:CS22" si="32">AG22*(1+$AI$27)</f>
         <v>1059.3337665765057</v>
       </c>
       <c r="AI22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1048.7404289107405</v>
       </c>
       <c r="AJ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1038.2530246216331</v>
       </c>
       <c r="AK22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1027.8704943754167</v>
       </c>
       <c r="AL22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1017.5917894316625</v>
       </c>
       <c r="AM22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1007.4158715373459</v>
       </c>
       <c r="AN22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>997.34171282197246</v>
       </c>
       <c r="AO22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>987.36829569375277</v>
       </c>
       <c r="AP22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>977.49461273681527</v>
       </c>
       <c r="AQ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>967.71966660944713</v>
       </c>
       <c r="AR22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>958.04246994335267</v>
       </c>
       <c r="AS22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>948.46204524391919</v>
       </c>
       <c r="AT22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>938.97742479147996</v>
       </c>
       <c r="AU22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>929.58765054356513</v>
       </c>
       <c r="AV22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>920.29177403812946</v>
       </c>
       <c r="AW22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>911.08885629774818</v>
       </c>
       <c r="AX22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>901.97796773477069</v>
       </c>
       <c r="AY22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>892.95818805742294</v>
       </c>
       <c r="AZ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>884.02860617684871</v>
       </c>
       <c r="BA22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>875.18832011508027</v>
       </c>
       <c r="BB22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>866.43643691392947</v>
       </c>
       <c r="BC22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>857.77207254479015</v>
       </c>
       <c r="BD22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>849.19435181934227</v>
       </c>
       <c r="BE22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>840.70240830114881</v>
       </c>
       <c r="BF22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>832.29538421813731</v>
       </c>
       <c r="BG22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>823.97243037595592</v>
       </c>
       <c r="BH22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>815.73270607219638</v>
       </c>
       <c r="BI22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>807.57537901147441</v>
       </c>
       <c r="BJ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>799.49962522135968</v>
       </c>
       <c r="BK22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>791.5046289691461</v>
       </c>
       <c r="BL22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>783.58958267945468</v>
       </c>
       <c r="BM22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>775.75368685266017</v>
       </c>
       <c r="BN22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>767.99614998413358</v>
       </c>
       <c r="BO22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>760.31618848429218</v>
       </c>
       <c r="BP22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>752.71302659944922</v>
       </c>
       <c r="BQ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>745.18589633345471</v>
       </c>
       <c r="BR22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>737.73403737012018</v>
       </c>
       <c r="BS22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>730.35669699641892</v>
       </c>
       <c r="BT22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>723.05313002645471</v>
       </c>
       <c r="BU22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>715.82259872619011</v>
       </c>
       <c r="BV22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>708.66437273892825</v>
       </c>
       <c r="BW22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>701.57772901153896</v>
       </c>
       <c r="BX22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>694.56195172142361</v>
       </c>
       <c r="BY22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>687.61633220420936</v>
       </c>
       <c r="BZ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>680.74016888216727</v>
       </c>
       <c r="CA22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>673.93276719334563</v>
       </c>
       <c r="CB22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>667.19343952141219</v>
       </c>
       <c r="CC22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>660.52150512619801</v>
       </c>
       <c r="CD22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>653.916290074936</v>
       </c>
       <c r="CE22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>647.37712717418663</v>
       </c>
       <c r="CF22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>640.90335590244479</v>
       </c>
       <c r="CG22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>634.49432234342032</v>
       </c>
       <c r="CH22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>628.14937911998607</v>
       </c>
       <c r="CI22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>621.8678853287862</v>
       </c>
       <c r="CJ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>615.64920647549832</v>
       </c>
       <c r="CK22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>609.49271441074336</v>
       </c>
       <c r="CL22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>603.39778726663587</v>
       </c>
       <c r="CM22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>597.36380939396952</v>
       </c>
       <c r="CN22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>591.39017130002981</v>
       </c>
       <c r="CO22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>585.47626958702949</v>
       </c>
       <c r="CP22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>579.62150689115924</v>
       </c>
       <c r="CQ22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>573.82529182224766</v>
       </c>
       <c r="CR22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>568.08703890402523</v>
       </c>
       <c r="CS22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>562.40616851498498</v>
       </c>
       <c r="CT22" s="2">
-        <f t="shared" ref="CT22:EJ22" si="25">CS22*(1+$AI$27)</f>
+        <f t="shared" ref="CT22:EJ22" si="33">CS22*(1+$AI$27)</f>
         <v>556.78210682983513</v>
       </c>
       <c r="CU22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>551.21428576153676</v>
       </c>
       <c r="CV22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>545.70214290392141</v>
       </c>
       <c r="CW22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>540.24512147488224</v>
       </c>
       <c r="CX22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>534.84267026013345</v>
       </c>
       <c r="CY22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>529.49424355753206</v>
       </c>
       <c r="CZ22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>524.19930112195675</v>
       </c>
       <c r="DA22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>518.95730811073713</v>
       </c>
       <c r="DB22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>513.76773502962976</v>
       </c>
       <c r="DC22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>508.63005767933345</v>
       </c>
       <c r="DD22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>503.5437571025401</v>
       </c>
       <c r="DE22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>498.5083195315147</v>
       </c>
       <c r="DF22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>493.52323633619955</v>
       </c>
       <c r="DG22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>488.58800397283756</v>
       </c>
       <c r="DH22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>483.70212393310919</v>
       </c>
       <c r="DI22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>478.86510269377811</v>
       </c>
       <c r="DJ22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>474.07645166684034</v>
       </c>
       <c r="DK22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>469.33568715017191</v>
       </c>
       <c r="DL22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>464.64233027867016</v>
       </c>
       <c r="DM22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>459.99590697588343</v>
       </c>
       <c r="DN22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>455.3959479061246</v>
       </c>
       <c r="DO22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>450.84198842706337</v>
       </c>
       <c r="DP22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>446.3335685427927</v>
       </c>
       <c r="DQ22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>441.87023285736478</v>
       </c>
       <c r="DR22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>437.45153052879112</v>
       </c>
       <c r="DS22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>433.07701522350322</v>
       </c>
       <c r="DT22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>428.74624507126816</v>
       </c>
       <c r="DU22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>424.4587826205555</v>
       </c>
       <c r="DV22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>420.21419479434996</v>
       </c>
       <c r="DW22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>416.01205284640645</v>
       </c>
       <c r="DX22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>411.85193231794238</v>
       </c>
       <c r="DY22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>407.73341299476294</v>
       </c>
       <c r="DZ22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>403.6560788648153</v>
       </c>
       <c r="EA22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>399.61951807616714</v>
       </c>
       <c r="EB22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>395.62332289540547</v>
       </c>
       <c r="EC22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>391.66708966645143</v>
       </c>
       <c r="ED22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>387.7504187697869</v>
       </c>
       <c r="EE22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>383.87291458208904</v>
       </c>
       <c r="EF22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>380.03418543626816</v>
       </c>
       <c r="EG22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>376.23384358190549</v>
       </c>
       <c r="EH22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>372.47150514608643</v>
       </c>
       <c r="EI22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>368.74679009462557</v>
       </c>
       <c r="EJ22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>365.05932219367929</v>
       </c>
     </row>
@@ -3479,113 +3500,113 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <f>734/4</f>
+        <f t="shared" ref="C23:L23" si="34">734/4</f>
         <v>183.5</v>
       </c>
       <c r="D23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="E23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="F23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="G23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="H23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="I23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="J23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="K23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="L23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="34"/>
         <v>183.5</v>
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
       <c r="P23" s="6">
-        <f>734/4</f>
+        <f t="shared" ref="P23:W23" si="35">734/4</f>
         <v>183.5</v>
       </c>
       <c r="Q23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="35"/>
         <v>183.5</v>
       </c>
       <c r="R23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="35"/>
         <v>183.5</v>
       </c>
       <c r="S23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="35"/>
         <v>183.5</v>
       </c>
       <c r="T23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="35"/>
         <v>183.5</v>
       </c>
       <c r="U23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="35"/>
         <v>183.5</v>
       </c>
       <c r="V23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="35"/>
         <v>183.5</v>
       </c>
       <c r="W23" s="6">
-        <f>734/4</f>
+        <f t="shared" si="35"/>
         <v>183.5</v>
       </c>
       <c r="X23" s="6">
-        <f t="shared" ref="X23:AF23" si="26">734/4</f>
+        <f t="shared" ref="X23:AF23" si="36">734/4</f>
         <v>183.5</v>
       </c>
       <c r="Y23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
       <c r="Z23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
       <c r="AA23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
       <c r="AB23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
       <c r="AC23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
       <c r="AD23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
       <c r="AE23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
       <c r="AF23" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>183.5</v>
       </c>
     </row>
@@ -3594,111 +3615,111 @@
         <v>41</v>
       </c>
       <c r="C24" s="8">
-        <f>C22/C23</f>
+        <f t="shared" ref="C24:L24" si="37">C22/C23</f>
         <v>-0.38692098092643035</v>
       </c>
       <c r="D24" s="8">
-        <f>D22/D23</f>
+        <f t="shared" si="37"/>
         <v>-0.10245231607629446</v>
       </c>
       <c r="E24" s="8">
-        <f>E22/E23</f>
+        <f t="shared" si="37"/>
         <v>0.33242506811989181</v>
       </c>
       <c r="F24" s="8">
-        <f>F22/F23</f>
+        <f t="shared" si="37"/>
         <v>1.0501362397820164</v>
       </c>
       <c r="G24" s="8">
-        <f>G22/G23</f>
+        <f t="shared" si="37"/>
         <v>0.15640326975476854</v>
       </c>
       <c r="H24" s="8">
-        <f>H22/H23</f>
+        <f t="shared" si="37"/>
         <v>0.54168937329700273</v>
       </c>
       <c r="I24" s="8">
-        <f>I22/I23</f>
+        <f t="shared" si="37"/>
         <v>0.97438692098092727</v>
       </c>
       <c r="J24" s="8">
-        <f>J22/J23</f>
+        <f t="shared" si="37"/>
         <v>0.24850136239781986</v>
       </c>
       <c r="K24" s="8">
-        <f>K22/K23</f>
+        <f t="shared" si="37"/>
         <v>0.40000000000000024</v>
       </c>
       <c r="L24" s="8">
-        <f>L22/L23</f>
+        <f t="shared" si="37"/>
         <v>0.42833787465940104</v>
       </c>
       <c r="P24" s="8">
-        <f>P22/P23</f>
+        <f t="shared" ref="P24:W24" si="38">P22/P23</f>
         <v>-1.7564032697547685</v>
       </c>
       <c r="Q24" s="8">
-        <f>Q22/Q23</f>
+        <f t="shared" si="38"/>
         <v>-3.9885558583106278</v>
       </c>
       <c r="R24" s="8">
-        <f>R22/R23</f>
+        <f t="shared" si="38"/>
         <v>-0.2435967302452324</v>
       </c>
       <c r="S24" s="8">
-        <f>S22/S23</f>
+        <f t="shared" si="38"/>
         <v>-1.0114441416893722</v>
       </c>
       <c r="T24" s="8">
-        <f>T22/T23</f>
+        <f t="shared" si="38"/>
         <v>0.89318801089918443</v>
       </c>
       <c r="U24" s="8">
-        <f>U22/U23</f>
+        <f t="shared" si="38"/>
         <v>1.2435967302452333</v>
       </c>
       <c r="V24" s="8">
-        <f>V22/V23</f>
+        <f t="shared" si="38"/>
         <v>4.052624414168938</v>
       </c>
       <c r="W24" s="8">
-        <f>W22/W23</f>
+        <f t="shared" si="38"/>
         <v>3.9196639283923713</v>
       </c>
       <c r="X24" s="8">
-        <f t="shared" ref="X24:AF24" si="27">X22/X23</f>
+        <f t="shared" ref="X24:AF24" si="39">X22/X23</f>
         <v>4.527528266019619</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>4.9393912976567966</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>5.2394391351610308</v>
       </c>
       <c r="AA24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>5.4056023669748594</v>
       </c>
       <c r="AB24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>5.4995692553031015</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>5.5949911266275718</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>5.6918843499650862</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>5.7902652397934968</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>5.8901500435033496</v>
       </c>
     </row>
@@ -3711,23 +3732,23 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10">
-        <f t="shared" ref="E26:K26" si="28">G3/C3-1</f>
+        <f t="shared" ref="G26:K26" si="40">G3/C3-1</f>
         <v>0.25101158085670439</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>0.15623307281590959</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>0.31765805045157269</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>0.17032049010176697</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>0.2302029890698194</v>
       </c>
       <c r="L26" s="10">
@@ -3735,28 +3756,28 @@
         <v>0.21750769642618129</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" ref="M26:N26" si="29">M3/I3-1</f>
+        <f t="shared" ref="M26:N26" si="41">M3/I3-1</f>
         <v>0.20999999999999996</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="P26" s="10"/>
       <c r="Q26" s="10">
-        <f t="shared" ref="P26:U26" si="30">Q3/P3-1</f>
+        <f t="shared" ref="Q26:T26" si="42">Q3/P3-1</f>
         <v>-0.30965108190239088</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0.11299090451062033</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>8.1721147431621066E-2</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0.16041143561957627</v>
       </c>
       <c r="U26" s="10">
@@ -3764,47 +3785,47 @@
         <v>0.21376103255195988</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" ref="V26:AF26" si="31">V3/U3-1</f>
+        <f t="shared" ref="V26:AF26" si="43">V3/U3-1</f>
         <v>0.21097221136253452</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3813,39 +3834,39 @@
         <v>45</v>
       </c>
       <c r="C27" s="10">
-        <f t="shared" ref="C27:L27" si="32">C5/C3</f>
+        <f t="shared" ref="C27:K27" si="44">C5/C3</f>
         <v>0.15864378401004608</v>
       </c>
       <c r="D27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.17279269519461424</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.18148551853005304</v>
       </c>
       <c r="F27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.17189003088451218</v>
       </c>
       <c r="G27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.18815525317867504</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.16062106813010307</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.18600803592531326</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.18585334198572351</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.17144152311876701</v>
       </c>
       <c r="L27" s="10">
@@ -3853,31 +3874,31 @@
         <v>0.19398636763412494</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" ref="M27:N27" si="33">M5/M3</f>
+        <f t="shared" ref="M27:N27" si="45">M5/M3</f>
         <v>0.19</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>0.19</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" ref="P27:U27" si="34">P5/P3</f>
+        <f t="shared" ref="P27:T27" si="46">P5/P3</f>
         <v>0.1456266246842163</v>
       </c>
       <c r="Q27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>0.12664739731112937</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>0.15715238730582293</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>0.20087220827276334</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>0.1726487615070704</v>
       </c>
       <c r="U27" s="10">
@@ -3885,47 +3906,47 @@
         <v>0.18032120349664568</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" ref="V27:AF27" si="35">V5/V3</f>
+        <f t="shared" ref="V27:AF27" si="47">V5/V3</f>
         <v>0.18829308696346139</v>
       </c>
       <c r="W27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="X27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="Y27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19000000000000003</v>
       </c>
       <c r="AE27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>0.19</v>
       </c>
       <c r="AH27" s="1" t="s">
@@ -3944,23 +3965,23 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10">
-        <f t="shared" ref="E28:K28" si="36">G6/C6-1</f>
+        <f t="shared" ref="G28:K28" si="48">G6/C6-1</f>
         <v>-5.9880239520958556E-3</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>-7.7972709551656916E-2</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>-6.6147859922178975E-2</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>3.2629558541266812E-2</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="48"/>
         <v>-1.2048192771084265E-2</v>
       </c>
       <c r="L28" s="10">
@@ -3968,28 +3989,28 @@
         <v>0.11416490486257946</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" ref="M28:N28" si="37">M6/I6-1</f>
+        <f t="shared" ref="M28:N28" si="49">M6/I6-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="P28" s="10"/>
       <c r="Q28" s="10">
-        <f t="shared" ref="P28:U28" si="38">Q6/P6-1</f>
+        <f t="shared" ref="Q28:T28" si="50">Q6/P6-1</f>
         <v>-0.24605678233438477</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="50"/>
         <v>6.8340306834030473E-2</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="50"/>
         <v>0.20691906005221949</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="50"/>
         <v>0.108166576527853</v>
       </c>
       <c r="U28" s="10">
@@ -3997,47 +4018,47 @@
         <v>-2.9282576866764387E-2</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" ref="V28:AF28" si="39">V6/U6-1</f>
+        <f t="shared" ref="V28:AF28" si="51">V6/U6-1</f>
         <v>3.9487179487179613E-2</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH28" s="1" t="s">
@@ -4052,39 +4073,39 @@
         <v>47</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:L29" si="40">C7/C3</f>
+        <f t="shared" ref="C29:K29" si="52">C7/C3</f>
         <v>9.5297893121250171E-2</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>6.4071809951249711E-2</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>5.6524447212706316E-2</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>4.6073616525745535E-2</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>8.5768458621458848E-2</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>5.0863338241199305E-2</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>4.6029307492318601E-2</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>3.413367942894225E-2</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="52"/>
         <v>6.4369900271985497E-2</v>
       </c>
       <c r="L29" s="10">
@@ -4092,31 +4113,31 @@
         <v>4.8867634124890064E-2</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" ref="M29:N29" si="41">M7/M3</f>
+        <f t="shared" ref="M29:N29" si="53">M7/M3</f>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="N29" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="53"/>
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" ref="P29:U29" si="42">P7/P3</f>
+        <f t="shared" ref="P29:T29" si="54">P7/P3</f>
         <v>5.2447552447552441E-2</v>
       </c>
       <c r="Q29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>5.1443875792209173E-2</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>5.3940722386352807E-2</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>6.0437866173296328E-2</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="54"/>
         <v>5.9732371642782577E-2</v>
       </c>
       <c r="U29" s="10">
@@ -4124,47 +4145,47 @@
         <v>4.8430731699688805E-2</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" ref="V29:AF29" si="43">V7/V3</f>
+        <f t="shared" ref="V29:AF29" si="55">V7/V3</f>
         <v>4.5085616836376539E-2</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.4000000000000004E-2</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="55"/>
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="AH29" s="1" t="s">
@@ -4184,23 +4205,23 @@
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10">
-        <f t="shared" ref="E30:K30" si="44">G9/C9-1</f>
+        <f t="shared" ref="G30:K30" si="56">G9/C9-1</f>
         <v>-0.61949685534591192</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="56"/>
         <v>-0.3571428571428571</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="56"/>
         <v>-0.43529411764705883</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="56"/>
         <v>1.6949152542372836E-2</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="56"/>
         <v>0.17355371900826433</v>
       </c>
       <c r="L30" s="10">
@@ -4208,28 +4229,28 @@
         <v>-0.20915032679738566</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" ref="M30:N30" si="45">M9/I9-1</f>
+        <f t="shared" ref="M30:N30" si="57">M9/I9-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="57"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="P30" s="10"/>
       <c r="Q30" s="10">
-        <f t="shared" ref="P30:U30" si="46">Q9/P9-1</f>
+        <f t="shared" ref="Q30:T30" si="58">Q9/P9-1</f>
         <v>-0.39676113360323884</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0.44295302013422821</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>1.558139534883721</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>-0.17909090909090908</v>
       </c>
       <c r="U30" s="10">
@@ -4237,47 +4258,47 @@
         <v>-0.39091915836101876</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" ref="V30:AF30" si="47">V9/U9-1</f>
+        <f t="shared" ref="V30:AF30" si="59">V9/U9-1</f>
         <v>3.0181818181818088E-2</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH30" s="1" t="s">
@@ -4293,39 +4314,39 @@
         <v>49</v>
       </c>
       <c r="C31" s="10">
-        <f t="shared" ref="C31:L31" si="48">C15/C3</f>
+        <f t="shared" ref="C31:K31" si="60">C15/C3</f>
         <v>-7.2973350076740592E-2</v>
       </c>
       <c r="D31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>5.6643194304727973E-2</v>
       </c>
       <c r="E31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>6.5711616318903876E-2</v>
       </c>
       <c r="F31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0.10586805731355374</v>
       </c>
       <c r="G31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>-4.3497657818424903E-3</v>
       </c>
       <c r="H31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>8.5597644224334093E-2</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0.16851808083195471</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0.11174561972744969</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>4.6418857660924795E-2</v>
       </c>
       <c r="L31" s="10">
@@ -4333,31 +4354,31 @@
         <v>9.8669744942832052E-2</v>
       </c>
       <c r="M31" s="10">
-        <f t="shared" ref="M31:N31" si="49">M15/M3</f>
+        <f t="shared" ref="M31:N31" si="61">M15/M3</f>
         <v>0</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" ref="P31:U31" si="50">P15/P3</f>
+        <f t="shared" ref="P31:T31" si="62">P15/P3</f>
         <v>-1.4095851792186869E-2</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>-8.575747129484769E-2</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>4.7960545125321621E-2</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>-2.4382185806792613E-2</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>5.9675429439119354E-2</v>
       </c>
       <c r="U31" s="10">
@@ -4365,47 +4386,47 @@
         <v>8.4945345364129704E-2</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" ref="V31:AF31" si="51">V15/V3</f>
+        <f t="shared" ref="V31:AF31" si="63">V15/V3</f>
         <v>0.10619542798345621</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11553340738748936</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.1177291978460487</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11878605026301885</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11930441121038989</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.1193044112103899</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11904268975166821</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11877840239629241</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11851152398841294</v>
       </c>
       <c r="AE31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11824202912555425</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0.11796989215619691</v>
       </c>
       <c r="AH31" s="1" t="s">
@@ -4421,39 +4442,39 @@
         <v>38</v>
       </c>
       <c r="C32" s="10">
-        <f t="shared" ref="C32:L32" si="52">C20/C19</f>
+        <f t="shared" ref="C32:K32" si="64">C20/C19</f>
         <v>0.29497098646034825</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>-31.62499999999876</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>-0.12412587412587381</v>
       </c>
       <c r="F32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>-0.18675417661097854</v>
       </c>
       <c r="G32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>1.8181818181818167E-2</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>7.9892280071813288E-2</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.25532786885245884</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>0.7746144721233692</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="64"/>
         <v>4.3112033195020842</v>
       </c>
       <c r="L32" s="10">
@@ -4461,31 +4482,31 @@
         <v>-0.46822033898304999</v>
       </c>
       <c r="M32" s="10" t="e">
-        <f t="shared" ref="M32:N32" si="53">M20/M19</f>
+        <f t="shared" ref="M32:N32" si="65">M20/M19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N32" s="10" t="e">
-        <f t="shared" si="53"/>
+        <f t="shared" si="65"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" ref="P32:U32" si="54">P20/P19</f>
+        <f t="shared" ref="P32:T32" si="66">P20/P19</f>
         <v>-0.6997851772287863</v>
       </c>
       <c r="Q32" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="66"/>
         <v>-0.14656801007556672</v>
       </c>
       <c r="R32" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="66"/>
         <v>2.5875912408759256</v>
       </c>
       <c r="S32" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="66"/>
         <v>1.1165048543689328E-2</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="66"/>
         <v>-0.36152570480928581</v>
       </c>
       <c r="U32" s="10">
@@ -4493,47 +4514,47 @@
         <v>0.46776057314536595</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" ref="V32:AF32" si="55">V20/V19</f>
+        <f t="shared" ref="V32:AF32" si="67">V20/V19</f>
         <v>-0.20495917262081192</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AB32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AC32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AD32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AE32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AF32" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AH32" s="1" t="s">
@@ -4549,39 +4570,39 @@
         <v>50</v>
       </c>
       <c r="C33" s="10">
-        <f t="shared" ref="C33:L33" si="56">C22/C3</f>
+        <f t="shared" ref="C33:K33" si="68">C22/C3</f>
         <v>-9.9065159760011109E-2</v>
       </c>
       <c r="D33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>-1.4547705641105033E-2</v>
       </c>
       <c r="E33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>4.7492992837122501E-2</v>
       </c>
       <c r="F33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>9.7564680269353457E-2</v>
       </c>
       <c r="G33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>3.2009814856123163E-2</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>6.6523892383884356E-2</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>0.10564878279366588</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>1.9727449707981806E-2</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="68"/>
         <v>6.6545784224841392E-2</v>
       </c>
       <c r="L33" s="10">
@@ -4589,31 +4610,31 @@
         <v>4.3205804749340417E-2</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" ref="M33:N33" si="57">M22/M3</f>
+        <f t="shared" ref="M33:N33" si="69">M22/M3</f>
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" ref="P33:U33" si="58">P22/P3</f>
+        <f t="shared" ref="P33:T33" si="70">P22/P3</f>
         <v>-5.9001208215867899E-2</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="70"/>
         <v>-0.19408130253772116</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="70"/>
         <v>-1.064995711426669E-2</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="70"/>
         <v>-4.0879256420421971E-2</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="70"/>
         <v>3.1109423934706337E-2</v>
       </c>
       <c r="U33" s="10">
@@ -4621,47 +4642,47 @@
         <v>3.5685802305033897E-2</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" ref="V33:AF33" si="59">V22/V3</f>
+        <f t="shared" ref="V33:AF33" si="71">V22/V3</f>
         <v>9.6032464148111202E-2</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.0766768739857414E-2</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.4046971240944332E-2</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.5694026960237979E-2</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.6571037073027032E-2</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.6715092533763E-2</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.6492629293849557E-2</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.6267985041780113E-2</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.6041138395082595E-2</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.5812067761652691E-2</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="71"/>
         <v>8.5580751337698976E-2</v>
       </c>
       <c r="AH33" s="1" t="s">
@@ -4669,7 +4690,7 @@
       </c>
       <c r="AI33" s="5">
         <f>Main!D3</f>
-        <v>57.19</v>
+        <v>57.35</v>
       </c>
     </row>
     <row r="34" spans="2:35" x14ac:dyDescent="0.3">
@@ -4678,7 +4699,7 @@
       </c>
       <c r="AI34" s="11">
         <f>AI32/AI33-1</f>
-        <v>-0.43120780386203839</v>
+        <v>-0.43279466962284185</v>
       </c>
     </row>
     <row r="35" spans="2:35" x14ac:dyDescent="0.3">
@@ -4687,6 +4708,33 @@
       </c>
       <c r="AI35" s="7" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="2:35" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="12">
+        <v>12070</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L38" s="13">
+        <f>Main!D9/Model!L36</f>
+        <v>0.92160107705053851</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L39" s="10">
+        <f>L36/Main!D9-1</f>
+        <v>8.5068176352795399E-2</v>
       </c>
     </row>
   </sheetData>
